--- a/Demand for each destination region.xlsx
+++ b/Demand for each destination region.xlsx
@@ -1,10 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\panat.000\Documents\Class\Term 6\Supply Chain Management\Game Stuff\Game Simulation\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83A963D-837A-4AC6-861D-738C1AB32629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet JS" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -14,29 +25,26 @@
     <t>day</t>
   </si>
   <si>
-    <t>Calopeia</t>
+    <t>calopeia</t>
   </si>
   <si>
-    <t>Sorange</t>
+    <t>sorange</t>
   </si>
   <si>
-    <t>Tyran</t>
+    <t>tyran</t>
   </si>
   <si>
-    <t>Entworpe</t>
+    <t>entworpe</t>
   </si>
   <si>
-    <t>Fardo</t>
+    <t>fardo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -66,13 +74,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,10 +413,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F731"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F863"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -420,7 +437,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -440,7 +457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -460,7 +477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -480,7 +497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -500,7 +517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -520,7 +537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -540,7 +557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -560,7 +577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -580,7 +597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -600,7 +617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -620,7 +637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -640,7 +657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -660,7 +677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -680,7 +697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -700,7 +717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -720,7 +737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -740,7 +757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -760,7 +777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -780,7 +797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -800,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -820,7 +837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -840,7 +857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -860,7 +877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -880,7 +897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -900,7 +917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -920,7 +937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -940,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -960,7 +977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -980,7 +997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1000,7 +1017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1020,7 +1037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1040,7 +1057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1060,7 +1077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1080,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1100,7 +1117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1120,7 +1137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1140,7 +1157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1160,7 +1177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1180,7 +1197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1200,7 +1217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1220,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1240,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1260,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1280,7 +1297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1300,7 +1317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1320,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1340,7 +1357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1360,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1380,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1400,7 +1417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1420,7 +1437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1440,7 +1457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -1460,7 +1477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -1480,7 +1497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -1500,7 +1517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -1520,7 +1537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -1540,7 +1557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -1560,7 +1577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -1580,7 +1597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -1600,7 +1617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -1620,7 +1637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -1640,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -1660,7 +1677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -1680,7 +1697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -1700,7 +1717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -1720,7 +1737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -1740,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -1760,7 +1777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -1780,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -1800,7 +1817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -1820,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -1840,7 +1857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -1860,7 +1877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -1880,7 +1897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -1900,7 +1917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -1920,7 +1937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -1940,7 +1957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -1960,7 +1977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -1980,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2000,7 +2017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2020,7 +2037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2040,7 +2057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2060,7 +2077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2080,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2100,7 +2117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2120,7 +2137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2140,7 +2157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2160,7 +2177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2180,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2200,7 +2217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2220,7 +2237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2240,7 +2257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2260,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2280,7 +2297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2300,7 +2317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2320,7 +2337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2340,7 +2357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2360,7 +2377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2380,7 +2397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2400,7 +2417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2420,7 +2437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2440,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2460,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -2480,7 +2497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -2500,7 +2517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -2520,7 +2537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -2540,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -2560,7 +2577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -2580,7 +2597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -2600,7 +2617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -2620,7 +2637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -2640,7 +2657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -2660,7 +2677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2680,7 +2697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -2700,7 +2717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2720,7 +2737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -2740,7 +2757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2760,7 +2777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2780,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -2800,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -2820,7 +2837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -2840,7 +2857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -2860,7 +2877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -2880,7 +2897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -2900,7 +2917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -2920,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -2940,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -2960,7 +2977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -2980,7 +2997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3000,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -3020,7 +3037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -3040,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -3060,7 +3077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -3080,7 +3097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -3100,7 +3117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -3120,7 +3137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -3140,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -3160,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -3180,7 +3197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -3200,7 +3217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -3220,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -3240,7 +3257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -3260,7 +3277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -3280,7 +3297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -3300,7 +3317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -3320,7 +3337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -3340,7 +3357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -3360,7 +3377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -3380,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -3400,7 +3417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -3420,7 +3437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -3440,7 +3457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -3460,7 +3477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -3480,7 +3497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -3500,7 +3517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -3520,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -3540,7 +3557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -3560,7 +3577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -3580,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -3600,7 +3617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -3620,7 +3637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -3640,7 +3657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -3660,7 +3677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -3680,7 +3697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -3700,7 +3717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -3720,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -3740,7 +3757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -3760,7 +3777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -3780,7 +3797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -3800,7 +3817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -3820,7 +3837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -3840,7 +3857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -3860,7 +3877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -3880,7 +3897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -3900,7 +3917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -3920,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -3940,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -3960,7 +3977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -3980,7 +3997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -4000,7 +4017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -4020,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -4040,7 +4057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -4060,7 +4077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -4080,7 +4097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -4100,7 +4117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -4120,7 +4137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -4140,7 +4157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -4160,7 +4177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -4180,7 +4197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -4200,7 +4217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -4220,7 +4237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -4240,7 +4257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -4260,7 +4277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -4280,7 +4297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -4300,7 +4317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -4320,7 +4337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -4340,7 +4357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -4360,7 +4377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -4380,7 +4397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -4400,7 +4417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -4420,7 +4437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -4440,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -4460,7 +4477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -4480,7 +4497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -4500,7 +4517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -4520,7 +4537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -4540,7 +4557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -4560,7 +4577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -4580,7 +4597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -4600,7 +4617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -4620,7 +4637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -4640,7 +4657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -4660,7 +4677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -4680,7 +4697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -4700,7 +4717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -4720,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -4740,7 +4757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -4760,7 +4777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -4780,7 +4797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -4800,7 +4817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -4820,7 +4837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -4840,7 +4857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -4860,7 +4877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -4880,7 +4897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -4900,7 +4917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -4920,7 +4937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -4940,7 +4957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -4960,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -4980,7 +4997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -5000,7 +5017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -5020,7 +5037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -5040,7 +5057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -5060,7 +5077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -5080,7 +5097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -5100,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -5120,7 +5137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -5140,7 +5157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -5160,7 +5177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -5180,7 +5197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -5200,7 +5217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -5220,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -5240,7 +5257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -5260,7 +5277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -5280,7 +5297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -5300,7 +5317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -5320,7 +5337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -5340,7 +5357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -5360,7 +5377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -5380,7 +5397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -5400,7 +5417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -5420,7 +5437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -5440,7 +5457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -5460,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -5480,7 +5497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -5500,7 +5517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -5520,7 +5537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -5540,7 +5557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -5560,7 +5577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -5580,7 +5597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -5600,7 +5617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -5620,7 +5637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -5640,7 +5657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -5660,7 +5677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -5680,7 +5697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -5700,7 +5717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
@@ -5720,7 +5737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>266</v>
       </c>
@@ -5740,7 +5757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>267</v>
       </c>
@@ -5760,7 +5777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>268</v>
       </c>
@@ -5780,7 +5797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>269</v>
       </c>
@@ -5800,7 +5817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>270</v>
       </c>
@@ -5820,7 +5837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>271</v>
       </c>
@@ -5840,7 +5857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>272</v>
       </c>
@@ -5860,7 +5877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>273</v>
       </c>
@@ -5880,7 +5897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>274</v>
       </c>
@@ -5900,7 +5917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>275</v>
       </c>
@@ -5920,7 +5937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>276</v>
       </c>
@@ -5940,7 +5957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>277</v>
       </c>
@@ -5960,7 +5977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>278</v>
       </c>
@@ -5980,7 +5997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>279</v>
       </c>
@@ -6000,7 +6017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>280</v>
       </c>
@@ -6020,7 +6037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>281</v>
       </c>
@@ -6040,7 +6057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>282</v>
       </c>
@@ -6060,7 +6077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>283</v>
       </c>
@@ -6080,7 +6097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>284</v>
       </c>
@@ -6100,7 +6117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>285</v>
       </c>
@@ -6120,7 +6137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>286</v>
       </c>
@@ -6140,7 +6157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>287</v>
       </c>
@@ -6160,7 +6177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>288</v>
       </c>
@@ -6180,7 +6197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>289</v>
       </c>
@@ -6200,7 +6217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>290</v>
       </c>
@@ -6220,7 +6237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>291</v>
       </c>
@@ -6240,7 +6257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>292</v>
       </c>
@@ -6260,7 +6277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>293</v>
       </c>
@@ -6280,7 +6297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>294</v>
       </c>
@@ -6300,7 +6317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>295</v>
       </c>
@@ -6320,7 +6337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>296</v>
       </c>
@@ -6340,7 +6357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>297</v>
       </c>
@@ -6360,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>298</v>
       </c>
@@ -6380,7 +6397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>299</v>
       </c>
@@ -6400,7 +6417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>300</v>
       </c>
@@ -6420,7 +6437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>301</v>
       </c>
@@ -6440,7 +6457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>302</v>
       </c>
@@ -6460,7 +6477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>303</v>
       </c>
@@ -6480,7 +6497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>304</v>
       </c>
@@ -6500,7 +6517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>305</v>
       </c>
@@ -6520,7 +6537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>306</v>
       </c>
@@ -6540,7 +6557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>307</v>
       </c>
@@ -6560,7 +6577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>308</v>
       </c>
@@ -6580,7 +6597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>309</v>
       </c>
@@ -6600,7 +6617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>310</v>
       </c>
@@ -6620,7 +6637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>311</v>
       </c>
@@ -6640,7 +6657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>312</v>
       </c>
@@ -6660,7 +6677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>313</v>
       </c>
@@ -6680,7 +6697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>314</v>
       </c>
@@ -6700,7 +6717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>315</v>
       </c>
@@ -6720,7 +6737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>316</v>
       </c>
@@ -6740,7 +6757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>317</v>
       </c>
@@ -6760,7 +6777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>318</v>
       </c>
@@ -6780,7 +6797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>319</v>
       </c>
@@ -6800,7 +6817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>320</v>
       </c>
@@ -6820,7 +6837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>321</v>
       </c>
@@ -6840,7 +6857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>322</v>
       </c>
@@ -6860,7 +6877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>323</v>
       </c>
@@ -6880,7 +6897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>324</v>
       </c>
@@ -6900,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>325</v>
       </c>
@@ -6920,7 +6937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>326</v>
       </c>
@@ -6940,7 +6957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>327</v>
       </c>
@@ -6960,7 +6977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>328</v>
       </c>
@@ -6980,7 +6997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>329</v>
       </c>
@@ -7000,7 +7017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>330</v>
       </c>
@@ -7020,7 +7037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>331</v>
       </c>
@@ -7040,7 +7057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>332</v>
       </c>
@@ -7060,7 +7077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>333</v>
       </c>
@@ -7080,7 +7097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>334</v>
       </c>
@@ -7100,7 +7117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>335</v>
       </c>
@@ -7120,7 +7137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>336</v>
       </c>
@@ -7140,7 +7157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>337</v>
       </c>
@@ -7160,7 +7177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>338</v>
       </c>
@@ -7180,7 +7197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>339</v>
       </c>
@@ -7200,7 +7217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>340</v>
       </c>
@@ -7220,7 +7237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>341</v>
       </c>
@@ -7240,7 +7257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>342</v>
       </c>
@@ -7260,7 +7277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>343</v>
       </c>
@@ -7280,7 +7297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>344</v>
       </c>
@@ -7300,7 +7317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>345</v>
       </c>
@@ -7320,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>346</v>
       </c>
@@ -7340,7 +7357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>347</v>
       </c>
@@ -7360,7 +7377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>348</v>
       </c>
@@ -7380,7 +7397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>349</v>
       </c>
@@ -7400,7 +7417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A351">
         <v>350</v>
       </c>
@@ -7420,7 +7437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A352">
         <v>351</v>
       </c>
@@ -7440,7 +7457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A353">
         <v>352</v>
       </c>
@@ -7460,7 +7477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A354">
         <v>353</v>
       </c>
@@ -7480,7 +7497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A355">
         <v>354</v>
       </c>
@@ -7500,7 +7517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A356">
         <v>355</v>
       </c>
@@ -7520,7 +7537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A357">
         <v>356</v>
       </c>
@@ -7540,7 +7557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A358">
         <v>357</v>
       </c>
@@ -7560,7 +7577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A359">
         <v>358</v>
       </c>
@@ -7580,7 +7597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A360">
         <v>359</v>
       </c>
@@ -7600,7 +7617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A361">
         <v>360</v>
       </c>
@@ -7620,7 +7637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A362">
         <v>361</v>
       </c>
@@ -7640,7 +7657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A363">
         <v>362</v>
       </c>
@@ -7660,7 +7677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A364">
         <v>363</v>
       </c>
@@ -7680,7 +7697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A365">
         <v>364</v>
       </c>
@@ -7700,7 +7717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A366">
         <v>365</v>
       </c>
@@ -7720,7 +7737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A367">
         <v>366</v>
       </c>
@@ -7740,7 +7757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A368">
         <v>367</v>
       </c>
@@ -7760,7 +7777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A369">
         <v>368</v>
       </c>
@@ -7780,7 +7797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A370">
         <v>369</v>
       </c>
@@ -7800,7 +7817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A371">
         <v>370</v>
       </c>
@@ -7820,7 +7837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A372">
         <v>371</v>
       </c>
@@ -7840,7 +7857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A373">
         <v>372</v>
       </c>
@@ -7860,7 +7877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A374">
         <v>373</v>
       </c>
@@ -7880,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A375">
         <v>374</v>
       </c>
@@ -7900,7 +7917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A376">
         <v>375</v>
       </c>
@@ -7920,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A377">
         <v>376</v>
       </c>
@@ -7940,7 +7957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A378">
         <v>377</v>
       </c>
@@ -7960,7 +7977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A379">
         <v>378</v>
       </c>
@@ -7980,7 +7997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A380">
         <v>379</v>
       </c>
@@ -8000,7 +8017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A381">
         <v>380</v>
       </c>
@@ -8020,7 +8037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A382">
         <v>381</v>
       </c>
@@ -8040,7 +8057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A383">
         <v>382</v>
       </c>
@@ -8060,7 +8077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A384">
         <v>383</v>
       </c>
@@ -8080,7 +8097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A385">
         <v>384</v>
       </c>
@@ -8100,7 +8117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A386">
         <v>385</v>
       </c>
@@ -8120,7 +8137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A387">
         <v>386</v>
       </c>
@@ -8140,7 +8157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A388">
         <v>387</v>
       </c>
@@ -8160,7 +8177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A389">
         <v>388</v>
       </c>
@@ -8180,7 +8197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A390">
         <v>389</v>
       </c>
@@ -8200,7 +8217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A391">
         <v>390</v>
       </c>
@@ -8220,7 +8237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A392">
         <v>391</v>
       </c>
@@ -8240,7 +8257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A393">
         <v>392</v>
       </c>
@@ -8260,7 +8277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A394">
         <v>393</v>
       </c>
@@ -8280,7 +8297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A395">
         <v>394</v>
       </c>
@@ -8300,7 +8317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A396">
         <v>395</v>
       </c>
@@ -8320,7 +8337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A397">
         <v>396</v>
       </c>
@@ -8340,7 +8357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A398">
         <v>397</v>
       </c>
@@ -8360,7 +8377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A399">
         <v>398</v>
       </c>
@@ -8380,7 +8397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A400">
         <v>399</v>
       </c>
@@ -8400,7 +8417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A401">
         <v>400</v>
       </c>
@@ -8420,7 +8437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A402">
         <v>401</v>
       </c>
@@ -8440,7 +8457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A403">
         <v>402</v>
       </c>
@@ -8460,7 +8477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A404">
         <v>403</v>
       </c>
@@ -8480,7 +8497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A405">
         <v>404</v>
       </c>
@@ -8500,7 +8517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A406">
         <v>405</v>
       </c>
@@ -8520,7 +8537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A407">
         <v>406</v>
       </c>
@@ -8540,7 +8557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A408">
         <v>407</v>
       </c>
@@ -8560,7 +8577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A409">
         <v>408</v>
       </c>
@@ -8580,7 +8597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A410">
         <v>409</v>
       </c>
@@ -8600,7 +8617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A411">
         <v>410</v>
       </c>
@@ -8620,7 +8637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A412">
         <v>411</v>
       </c>
@@ -8640,7 +8657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A413">
         <v>412</v>
       </c>
@@ -8660,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A414">
         <v>413</v>
       </c>
@@ -8680,7 +8697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A415">
         <v>414</v>
       </c>
@@ -8700,7 +8717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A416">
         <v>415</v>
       </c>
@@ -8720,7 +8737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A417">
         <v>416</v>
       </c>
@@ -8740,7 +8757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A418">
         <v>417</v>
       </c>
@@ -8760,7 +8777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A419">
         <v>418</v>
       </c>
@@ -8780,7 +8797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A420">
         <v>419</v>
       </c>
@@ -8800,7 +8817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A421">
         <v>420</v>
       </c>
@@ -8820,7 +8837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A422">
         <v>421</v>
       </c>
@@ -8840,7 +8857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A423">
         <v>422</v>
       </c>
@@ -8860,7 +8877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A424">
         <v>423</v>
       </c>
@@ -8880,7 +8897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A425">
         <v>424</v>
       </c>
@@ -8900,7 +8917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A426">
         <v>425</v>
       </c>
@@ -8920,7 +8937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A427">
         <v>426</v>
       </c>
@@ -8940,7 +8957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A428">
         <v>427</v>
       </c>
@@ -8960,7 +8977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A429">
         <v>428</v>
       </c>
@@ -8980,7 +8997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A430">
         <v>429</v>
       </c>
@@ -9000,7 +9017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A431">
         <v>430</v>
       </c>
@@ -9020,7 +9037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A432">
         <v>431</v>
       </c>
@@ -9040,7 +9057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A433">
         <v>432</v>
       </c>
@@ -9060,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A434">
         <v>433</v>
       </c>
@@ -9080,7 +9097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A435">
         <v>434</v>
       </c>
@@ -9100,7 +9117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A436">
         <v>435</v>
       </c>
@@ -9120,7 +9137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A437">
         <v>436</v>
       </c>
@@ -9140,7 +9157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A438">
         <v>437</v>
       </c>
@@ -9160,7 +9177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A439">
         <v>438</v>
       </c>
@@ -9180,7 +9197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A440">
         <v>439</v>
       </c>
@@ -9200,7 +9217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A441">
         <v>440</v>
       </c>
@@ -9220,7 +9237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A442">
         <v>441</v>
       </c>
@@ -9240,7 +9257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A443">
         <v>442</v>
       </c>
@@ -9260,7 +9277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A444">
         <v>443</v>
       </c>
@@ -9280,7 +9297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A445">
         <v>444</v>
       </c>
@@ -9300,7 +9317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A446">
         <v>445</v>
       </c>
@@ -9320,7 +9337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A447">
         <v>446</v>
       </c>
@@ -9340,7 +9357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A448">
         <v>447</v>
       </c>
@@ -9360,7 +9377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A449">
         <v>448</v>
       </c>
@@ -9380,7 +9397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A450">
         <v>449</v>
       </c>
@@ -9400,7 +9417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A451">
         <v>450</v>
       </c>
@@ -9420,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A452">
         <v>451</v>
       </c>
@@ -9440,7 +9457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A453">
         <v>452</v>
       </c>
@@ -9460,7 +9477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A454">
         <v>453</v>
       </c>
@@ -9480,7 +9497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A455">
         <v>454</v>
       </c>
@@ -9500,7 +9517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A456">
         <v>455</v>
       </c>
@@ -9520,7 +9537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A457">
         <v>456</v>
       </c>
@@ -9540,7 +9557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A458">
         <v>457</v>
       </c>
@@ -9560,7 +9577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A459">
         <v>458</v>
       </c>
@@ -9580,7 +9597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A460">
         <v>459</v>
       </c>
@@ -9600,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A461">
         <v>460</v>
       </c>
@@ -9620,7 +9637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A462">
         <v>461</v>
       </c>
@@ -9640,7 +9657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A463">
         <v>462</v>
       </c>
@@ -9660,7 +9677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A464">
         <v>463</v>
       </c>
@@ -9680,7 +9697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A465">
         <v>464</v>
       </c>
@@ -9700,7 +9717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A466">
         <v>465</v>
       </c>
@@ -9720,7 +9737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A467">
         <v>466</v>
       </c>
@@ -9740,7 +9757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A468">
         <v>467</v>
       </c>
@@ -9760,7 +9777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A469">
         <v>468</v>
       </c>
@@ -9780,7 +9797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A470">
         <v>469</v>
       </c>
@@ -9800,7 +9817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A471">
         <v>470</v>
       </c>
@@ -9820,7 +9837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A472">
         <v>471</v>
       </c>
@@ -9840,7 +9857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A473">
         <v>472</v>
       </c>
@@ -9860,7 +9877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A474">
         <v>473</v>
       </c>
@@ -9880,7 +9897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A475">
         <v>474</v>
       </c>
@@ -9900,7 +9917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A476">
         <v>475</v>
       </c>
@@ -9920,7 +9937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A477">
         <v>476</v>
       </c>
@@ -9940,7 +9957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A478">
         <v>477</v>
       </c>
@@ -9960,7 +9977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A479">
         <v>478</v>
       </c>
@@ -9980,7 +9997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A480">
         <v>479</v>
       </c>
@@ -10000,7 +10017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A481">
         <v>480</v>
       </c>
@@ -10020,7 +10037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A482">
         <v>481</v>
       </c>
@@ -10040,7 +10057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A483">
         <v>482</v>
       </c>
@@ -10060,7 +10077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A484">
         <v>483</v>
       </c>
@@ -10080,7 +10097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A485">
         <v>484</v>
       </c>
@@ -10100,7 +10117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A486">
         <v>485</v>
       </c>
@@ -10120,7 +10137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A487">
         <v>486</v>
       </c>
@@ -10140,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A488">
         <v>487</v>
       </c>
@@ -10160,7 +10177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A489">
         <v>488</v>
       </c>
@@ -10180,7 +10197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A490">
         <v>489</v>
       </c>
@@ -10200,7 +10217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A491">
         <v>490</v>
       </c>
@@ -10220,7 +10237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A492">
         <v>491</v>
       </c>
@@ -10240,7 +10257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A493">
         <v>492</v>
       </c>
@@ -10260,7 +10277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A494">
         <v>493</v>
       </c>
@@ -10280,7 +10297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A495">
         <v>494</v>
       </c>
@@ -10300,7 +10317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A496">
         <v>495</v>
       </c>
@@ -10320,7 +10337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A497">
         <v>496</v>
       </c>
@@ -10340,7 +10357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A498">
         <v>497</v>
       </c>
@@ -10360,7 +10377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A499">
         <v>498</v>
       </c>
@@ -10380,7 +10397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A500">
         <v>499</v>
       </c>
@@ -10400,7 +10417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A501">
         <v>500</v>
       </c>
@@ -10420,7 +10437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A502">
         <v>501</v>
       </c>
@@ -10440,7 +10457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A503">
         <v>502</v>
       </c>
@@ -10460,7 +10477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A504">
         <v>503</v>
       </c>
@@ -10480,7 +10497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A505">
         <v>504</v>
       </c>
@@ -10500,7 +10517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A506">
         <v>505</v>
       </c>
@@ -10520,7 +10537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A507">
         <v>506</v>
       </c>
@@ -10540,7 +10557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A508">
         <v>507</v>
       </c>
@@ -10560,7 +10577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A509">
         <v>508</v>
       </c>
@@ -10580,7 +10597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A510">
         <v>509</v>
       </c>
@@ -10600,7 +10617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A511">
         <v>510</v>
       </c>
@@ -10620,7 +10637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A512">
         <v>511</v>
       </c>
@@ -10640,7 +10657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A513">
         <v>512</v>
       </c>
@@ -10660,7 +10677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A514">
         <v>513</v>
       </c>
@@ -10680,7 +10697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A515">
         <v>514</v>
       </c>
@@ -10700,7 +10717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A516">
         <v>515</v>
       </c>
@@ -10720,7 +10737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A517">
         <v>516</v>
       </c>
@@ -10740,7 +10757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A518">
         <v>517</v>
       </c>
@@ -10760,7 +10777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A519">
         <v>518</v>
       </c>
@@ -10780,7 +10797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A520">
         <v>519</v>
       </c>
@@ -10800,7 +10817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A521">
         <v>520</v>
       </c>
@@ -10820,7 +10837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522">
+    <row r="522" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A522">
         <v>521</v>
       </c>
@@ -10840,7 +10857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A523">
         <v>522</v>
       </c>
@@ -10860,7 +10877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A524">
         <v>523</v>
       </c>
@@ -10880,7 +10897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A525">
         <v>524</v>
       </c>
@@ -10900,7 +10917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A526">
         <v>525</v>
       </c>
@@ -10920,7 +10937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A527">
         <v>526</v>
       </c>
@@ -10940,7 +10957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528">
+    <row r="528" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A528">
         <v>527</v>
       </c>
@@ -10960,7 +10977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A529">
         <v>528</v>
       </c>
@@ -10980,7 +10997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A530">
         <v>529</v>
       </c>
@@ -11000,7 +11017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531">
+    <row r="531" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A531">
         <v>530</v>
       </c>
@@ -11020,7 +11037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532">
+    <row r="532" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A532">
         <v>531</v>
       </c>
@@ -11040,7 +11057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A533">
         <v>532</v>
       </c>
@@ -11060,7 +11077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A534">
         <v>533</v>
       </c>
@@ -11080,7 +11097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A535">
         <v>534</v>
       </c>
@@ -11100,7 +11117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A536">
         <v>535</v>
       </c>
@@ -11120,7 +11137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A537">
         <v>536</v>
       </c>
@@ -11140,7 +11157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A538">
         <v>537</v>
       </c>
@@ -11160,7 +11177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539">
+    <row r="539" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A539">
         <v>538</v>
       </c>
@@ -11180,7 +11197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A540">
         <v>539</v>
       </c>
@@ -11200,7 +11217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541">
+    <row r="541" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A541">
         <v>540</v>
       </c>
@@ -11220,7 +11237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A542">
         <v>541</v>
       </c>
@@ -11240,7 +11257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A543">
         <v>542</v>
       </c>
@@ -11260,7 +11277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A544">
         <v>543</v>
       </c>
@@ -11280,7 +11297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A545">
         <v>544</v>
       </c>
@@ -11300,7 +11317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A546">
         <v>545</v>
       </c>
@@ -11320,7 +11337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A547">
         <v>546</v>
       </c>
@@ -11340,7 +11357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A548">
         <v>547</v>
       </c>
@@ -11360,7 +11377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A549">
         <v>548</v>
       </c>
@@ -11380,7 +11397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A550">
         <v>549</v>
       </c>
@@ -11400,7 +11417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A551">
         <v>550</v>
       </c>
@@ -11420,7 +11437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="552">
+    <row r="552" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A552">
         <v>551</v>
       </c>
@@ -11440,7 +11457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A553">
         <v>552</v>
       </c>
@@ -11460,7 +11477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="554">
+    <row r="554" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A554">
         <v>553</v>
       </c>
@@ -11480,7 +11497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A555">
         <v>554</v>
       </c>
@@ -11500,7 +11517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A556">
         <v>555</v>
       </c>
@@ -11520,7 +11537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="557">
+    <row r="557" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A557">
         <v>556</v>
       </c>
@@ -11540,7 +11557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A558">
         <v>557</v>
       </c>
@@ -11560,7 +11577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A559">
         <v>558</v>
       </c>
@@ -11580,7 +11597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560">
+    <row r="560" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A560">
         <v>559</v>
       </c>
@@ -11600,7 +11617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A561">
         <v>560</v>
       </c>
@@ -11620,7 +11637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A562">
         <v>561</v>
       </c>
@@ -11640,7 +11657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A563">
         <v>562</v>
       </c>
@@ -11660,7 +11677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A564">
         <v>563</v>
       </c>
@@ -11680,7 +11697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A565">
         <v>564</v>
       </c>
@@ -11700,7 +11717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A566">
         <v>565</v>
       </c>
@@ -11720,7 +11737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A567">
         <v>566</v>
       </c>
@@ -11740,7 +11757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A568">
         <v>567</v>
       </c>
@@ -11760,7 +11777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569">
+    <row r="569" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A569">
         <v>568</v>
       </c>
@@ -11780,7 +11797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A570">
         <v>569</v>
       </c>
@@ -11800,7 +11817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A571">
         <v>570</v>
       </c>
@@ -11820,7 +11837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A572">
         <v>571</v>
       </c>
@@ -11840,7 +11857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="573">
+    <row r="573" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A573">
         <v>572</v>
       </c>
@@ -11860,7 +11877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A574">
         <v>573</v>
       </c>
@@ -11880,7 +11897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A575">
         <v>574</v>
       </c>
@@ -11900,7 +11917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576">
+    <row r="576" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A576">
         <v>575</v>
       </c>
@@ -11920,7 +11937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A577">
         <v>576</v>
       </c>
@@ -11940,7 +11957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A578">
         <v>577</v>
       </c>
@@ -11960,7 +11977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A579">
         <v>578</v>
       </c>
@@ -11980,7 +11997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A580">
         <v>579</v>
       </c>
@@ -12000,7 +12017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A581">
         <v>580</v>
       </c>
@@ -12020,7 +12037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="582">
+    <row r="582" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A582">
         <v>581</v>
       </c>
@@ -12040,7 +12057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="583">
+    <row r="583" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A583">
         <v>582</v>
       </c>
@@ -12060,7 +12077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A584">
         <v>583</v>
       </c>
@@ -12080,7 +12097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="585">
+    <row r="585" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A585">
         <v>584</v>
       </c>
@@ -12100,7 +12117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="586">
+    <row r="586" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A586">
         <v>585</v>
       </c>
@@ -12120,7 +12137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="587">
+    <row r="587" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A587">
         <v>586</v>
       </c>
@@ -12140,7 +12157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588">
+    <row r="588" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A588">
         <v>587</v>
       </c>
@@ -12160,7 +12177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589">
+    <row r="589" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A589">
         <v>588</v>
       </c>
@@ -12180,7 +12197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590">
+    <row r="590" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A590">
         <v>589</v>
       </c>
@@ -12200,7 +12217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="591">
+    <row r="591" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A591">
         <v>590</v>
       </c>
@@ -12220,7 +12237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="592">
+    <row r="592" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A592">
         <v>591</v>
       </c>
@@ -12240,7 +12257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593">
+    <row r="593" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A593">
         <v>592</v>
       </c>
@@ -12260,7 +12277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594">
+    <row r="594" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A594">
         <v>593</v>
       </c>
@@ -12280,7 +12297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="595">
+    <row r="595" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A595">
         <v>594</v>
       </c>
@@ -12300,7 +12317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="596">
+    <row r="596" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A596">
         <v>595</v>
       </c>
@@ -12320,7 +12337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597">
+    <row r="597" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A597">
         <v>596</v>
       </c>
@@ -12340,7 +12357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598">
+    <row r="598" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A598">
         <v>597</v>
       </c>
@@ -12360,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599">
+    <row r="599" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A599">
         <v>598</v>
       </c>
@@ -12380,7 +12397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600">
+    <row r="600" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A600">
         <v>599</v>
       </c>
@@ -12400,7 +12417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601">
+    <row r="601" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A601">
         <v>600</v>
       </c>
@@ -12420,7 +12437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="602">
+    <row r="602" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A602">
         <v>601</v>
       </c>
@@ -12440,7 +12457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603">
+    <row r="603" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A603">
         <v>602</v>
       </c>
@@ -12460,7 +12477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="604">
+    <row r="604" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A604">
         <v>603</v>
       </c>
@@ -12480,7 +12497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="605">
+    <row r="605" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A605">
         <v>604</v>
       </c>
@@ -12500,7 +12517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="606">
+    <row r="606" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A606">
         <v>605</v>
       </c>
@@ -12520,7 +12537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="607">
+    <row r="607" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A607">
         <v>606</v>
       </c>
@@ -12540,7 +12557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="608">
+    <row r="608" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A608">
         <v>607</v>
       </c>
@@ -12560,7 +12577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="609">
+    <row r="609" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A609">
         <v>608</v>
       </c>
@@ -12580,7 +12597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="610">
+    <row r="610" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A610">
         <v>609</v>
       </c>
@@ -12600,7 +12617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="611">
+    <row r="611" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A611">
         <v>610</v>
       </c>
@@ -12620,7 +12637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612">
+    <row r="612" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A612">
         <v>611</v>
       </c>
@@ -12640,7 +12657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="613">
+    <row r="613" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A613">
         <v>612</v>
       </c>
@@ -12660,7 +12677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="614">
+    <row r="614" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A614">
         <v>613</v>
       </c>
@@ -12680,7 +12697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="615">
+    <row r="615" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A615">
         <v>614</v>
       </c>
@@ -12700,7 +12717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616">
+    <row r="616" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A616">
         <v>615</v>
       </c>
@@ -12720,7 +12737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617">
+    <row r="617" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A617">
         <v>616</v>
       </c>
@@ -12740,7 +12757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618">
+    <row r="618" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A618">
         <v>617</v>
       </c>
@@ -12760,7 +12777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="619">
+    <row r="619" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A619">
         <v>618</v>
       </c>
@@ -12780,7 +12797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="620">
+    <row r="620" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A620">
         <v>619</v>
       </c>
@@ -12800,7 +12817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621">
+    <row r="621" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A621">
         <v>620</v>
       </c>
@@ -12820,7 +12837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="622">
+    <row r="622" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A622">
         <v>621</v>
       </c>
@@ -12840,7 +12857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623">
+    <row r="623" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A623">
         <v>622</v>
       </c>
@@ -12860,7 +12877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="624">
+    <row r="624" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A624">
         <v>623</v>
       </c>
@@ -12880,7 +12897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="625">
+    <row r="625" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A625">
         <v>624</v>
       </c>
@@ -12900,7 +12917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626">
+    <row r="626" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A626">
         <v>625</v>
       </c>
@@ -12920,7 +12937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627">
+    <row r="627" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A627">
         <v>626</v>
       </c>
@@ -12940,7 +12957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628">
+    <row r="628" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A628">
         <v>627</v>
       </c>
@@ -12960,7 +12977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629">
+    <row r="629" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A629">
         <v>628</v>
       </c>
@@ -12980,7 +12997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630">
+    <row r="630" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A630">
         <v>629</v>
       </c>
@@ -13000,7 +13017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="631">
+    <row r="631" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A631">
         <v>630</v>
       </c>
@@ -13020,7 +13037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="632">
+    <row r="632" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A632">
         <v>631</v>
       </c>
@@ -13040,7 +13057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="633">
+    <row r="633" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A633">
         <v>632</v>
       </c>
@@ -13060,7 +13077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="634">
+    <row r="634" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A634">
         <v>633</v>
       </c>
@@ -13080,7 +13097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="635">
+    <row r="635" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A635">
         <v>634</v>
       </c>
@@ -13100,7 +13117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="636">
+    <row r="636" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A636">
         <v>635</v>
       </c>
@@ -13120,7 +13137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="637">
+    <row r="637" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A637">
         <v>636</v>
       </c>
@@ -13140,7 +13157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="638">
+    <row r="638" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A638">
         <v>637</v>
       </c>
@@ -13160,7 +13177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="639">
+    <row r="639" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A639">
         <v>638</v>
       </c>
@@ -13180,7 +13197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="640">
+    <row r="640" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A640">
         <v>639</v>
       </c>
@@ -13200,7 +13217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="641">
+    <row r="641" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A641">
         <v>640</v>
       </c>
@@ -13220,7 +13237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="642">
+    <row r="642" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A642">
         <v>641</v>
       </c>
@@ -13240,7 +13257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="643">
+    <row r="643" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A643">
         <v>642</v>
       </c>
@@ -13260,7 +13277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="644">
+    <row r="644" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A644">
         <v>643</v>
       </c>
@@ -13280,7 +13297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="645">
+    <row r="645" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A645">
         <v>644</v>
       </c>
@@ -13300,7 +13317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="646">
+    <row r="646" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A646">
         <v>645</v>
       </c>
@@ -13320,7 +13337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="647">
+    <row r="647" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A647">
         <v>646</v>
       </c>
@@ -13340,7 +13357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="648">
+    <row r="648" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A648">
         <v>647</v>
       </c>
@@ -13360,7 +13377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="649">
+    <row r="649" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A649">
         <v>648</v>
       </c>
@@ -13380,7 +13397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="650">
+    <row r="650" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A650">
         <v>649</v>
       </c>
@@ -13400,7 +13417,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="651">
+    <row r="651" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A651">
         <v>650</v>
       </c>
@@ -13420,7 +13437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652">
+    <row r="652" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A652">
         <v>651</v>
       </c>
@@ -13440,7 +13457,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="653">
+    <row r="653" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A653">
         <v>652</v>
       </c>
@@ -13460,7 +13477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="654">
+    <row r="654" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A654">
         <v>653</v>
       </c>
@@ -13480,7 +13497,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="655">
+    <row r="655" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A655">
         <v>654</v>
       </c>
@@ -13500,7 +13517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="656">
+    <row r="656" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A656">
         <v>655</v>
       </c>
@@ -13520,7 +13537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="657">
+    <row r="657" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A657">
         <v>656</v>
       </c>
@@ -13540,7 +13557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="658">
+    <row r="658" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A658">
         <v>657</v>
       </c>
@@ -13560,7 +13577,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="659">
+    <row r="659" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A659">
         <v>658</v>
       </c>
@@ -13580,7 +13597,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="660">
+    <row r="660" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A660">
         <v>659</v>
       </c>
@@ -13600,7 +13617,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="661">
+    <row r="661" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A661">
         <v>660</v>
       </c>
@@ -13620,7 +13637,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="662">
+    <row r="662" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A662">
         <v>661</v>
       </c>
@@ -13640,7 +13657,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="663">
+    <row r="663" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A663">
         <v>662</v>
       </c>
@@ -13660,7 +13677,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="664">
+    <row r="664" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A664">
         <v>663</v>
       </c>
@@ -13680,7 +13697,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="665">
+    <row r="665" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A665">
         <v>664</v>
       </c>
@@ -13700,7 +13717,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="666">
+    <row r="666" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A666">
         <v>665</v>
       </c>
@@ -13720,7 +13737,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="667">
+    <row r="667" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A667">
         <v>666</v>
       </c>
@@ -13740,7 +13757,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="668">
+    <row r="668" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A668">
         <v>667</v>
       </c>
@@ -13760,7 +13777,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="669">
+    <row r="669" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A669">
         <v>668</v>
       </c>
@@ -13780,7 +13797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="670">
+    <row r="670" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A670">
         <v>669</v>
       </c>
@@ -13800,7 +13817,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="671">
+    <row r="671" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A671">
         <v>670</v>
       </c>
@@ -13820,7 +13837,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="672">
+    <row r="672" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A672">
         <v>671</v>
       </c>
@@ -13840,7 +13857,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="673">
+    <row r="673" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A673">
         <v>672</v>
       </c>
@@ -13860,7 +13877,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="674">
+    <row r="674" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A674">
         <v>673</v>
       </c>
@@ -13880,7 +13897,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="675">
+    <row r="675" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A675">
         <v>674</v>
       </c>
@@ -13900,7 +13917,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="676">
+    <row r="676" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A676">
         <v>675</v>
       </c>
@@ -13920,7 +13937,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="677">
+    <row r="677" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A677">
         <v>676</v>
       </c>
@@ -13940,7 +13957,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="678">
+    <row r="678" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A678">
         <v>677</v>
       </c>
@@ -13960,7 +13977,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="679">
+    <row r="679" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A679">
         <v>678</v>
       </c>
@@ -13980,7 +13997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="680">
+    <row r="680" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A680">
         <v>679</v>
       </c>
@@ -14000,7 +14017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681">
+    <row r="681" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A681">
         <v>680</v>
       </c>
@@ -14020,7 +14037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="682">
+    <row r="682" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A682">
         <v>681</v>
       </c>
@@ -14040,7 +14057,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="683">
+    <row r="683" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A683">
         <v>682</v>
       </c>
@@ -14060,7 +14077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684">
+    <row r="684" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A684">
         <v>683</v>
       </c>
@@ -14080,7 +14097,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="685">
+    <row r="685" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A685">
         <v>684</v>
       </c>
@@ -14100,7 +14117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686">
+    <row r="686" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A686">
         <v>685</v>
       </c>
@@ -14120,7 +14137,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="687">
+    <row r="687" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A687">
         <v>686</v>
       </c>
@@ -14140,7 +14157,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="688">
+    <row r="688" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A688">
         <v>687</v>
       </c>
@@ -14160,7 +14177,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="689">
+    <row r="689" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A689">
         <v>688</v>
       </c>
@@ -14180,7 +14197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="690">
+    <row r="690" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A690">
         <v>689</v>
       </c>
@@ -14200,7 +14217,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="691">
+    <row r="691" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A691">
         <v>690</v>
       </c>
@@ -14220,7 +14237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="692">
+    <row r="692" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A692">
         <v>691</v>
       </c>
@@ -14240,7 +14257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="693">
+    <row r="693" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A693">
         <v>692</v>
       </c>
@@ -14260,7 +14277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="694">
+    <row r="694" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A694">
         <v>693</v>
       </c>
@@ -14280,7 +14297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="695">
+    <row r="695" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A695">
         <v>694</v>
       </c>
@@ -14300,7 +14317,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="696">
+    <row r="696" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A696">
         <v>695</v>
       </c>
@@ -14320,7 +14337,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="697">
+    <row r="697" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A697">
         <v>696</v>
       </c>
@@ -14340,7 +14357,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="698">
+    <row r="698" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A698">
         <v>697</v>
       </c>
@@ -14360,7 +14377,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="699">
+    <row r="699" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A699">
         <v>698</v>
       </c>
@@ -14380,7 +14397,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="700">
+    <row r="700" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A700">
         <v>699</v>
       </c>
@@ -14400,7 +14417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="701">
+    <row r="701" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A701">
         <v>700</v>
       </c>
@@ -14420,7 +14437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="702">
+    <row r="702" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A702">
         <v>701</v>
       </c>
@@ -14440,7 +14457,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="703">
+    <row r="703" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A703">
         <v>702</v>
       </c>
@@ -14460,7 +14477,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="704">
+    <row r="704" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A704">
         <v>703</v>
       </c>
@@ -14480,7 +14497,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="705">
+    <row r="705" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A705">
         <v>704</v>
       </c>
@@ -14500,7 +14517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="706">
+    <row r="706" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A706">
         <v>705</v>
       </c>
@@ -14520,7 +14537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="707">
+    <row r="707" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A707">
         <v>706</v>
       </c>
@@ -14540,7 +14557,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="708">
+    <row r="708" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A708">
         <v>707</v>
       </c>
@@ -14560,7 +14577,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="709">
+    <row r="709" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A709">
         <v>708</v>
       </c>
@@ -14580,7 +14597,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="710">
+    <row r="710" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A710">
         <v>709</v>
       </c>
@@ -14600,7 +14617,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="711">
+    <row r="711" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A711">
         <v>710</v>
       </c>
@@ -14620,7 +14637,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="712">
+    <row r="712" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A712">
         <v>711</v>
       </c>
@@ -14640,7 +14657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713">
+    <row r="713" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A713">
         <v>712</v>
       </c>
@@ -14660,7 +14677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="714">
+    <row r="714" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A714">
         <v>713</v>
       </c>
@@ -14680,7 +14697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715">
+    <row r="715" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A715">
         <v>714</v>
       </c>
@@ -14700,7 +14717,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="716">
+    <row r="716" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A716">
         <v>715</v>
       </c>
@@ -14720,7 +14737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717">
+    <row r="717" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A717">
         <v>716</v>
       </c>
@@ -14740,7 +14757,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="718">
+    <row r="718" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A718">
         <v>717</v>
       </c>
@@ -14760,7 +14777,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="719">
+    <row r="719" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A719">
         <v>718</v>
       </c>
@@ -14780,7 +14797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="720">
+    <row r="720" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A720">
         <v>719</v>
       </c>
@@ -14800,7 +14817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="721">
+    <row r="721" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A721">
         <v>720</v>
       </c>
@@ -14820,7 +14837,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="722">
+    <row r="722" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A722">
         <v>721</v>
       </c>
@@ -14840,7 +14857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="723">
+    <row r="723" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A723">
         <v>722</v>
       </c>
@@ -14860,7 +14877,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="724">
+    <row r="724" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A724">
         <v>723</v>
       </c>
@@ -14880,7 +14897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="725">
+    <row r="725" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A725">
         <v>724</v>
       </c>
@@ -14900,7 +14917,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="726">
+    <row r="726" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A726">
         <v>725</v>
       </c>
@@ -14920,7 +14937,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="727">
+    <row r="727" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A727">
         <v>726</v>
       </c>
@@ -14940,7 +14957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="728">
+    <row r="728" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A728">
         <v>727</v>
       </c>
@@ -14960,7 +14977,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="729">
+    <row r="729" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A729">
         <v>728</v>
       </c>
@@ -14980,7 +14997,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="730">
+    <row r="730" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A730">
         <v>729</v>
       </c>
@@ -15000,7 +15017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="731">
+    <row r="731" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A731">
         <v>730</v>
       </c>
@@ -15020,9 +15037,2650 @@
         <v>3</v>
       </c>
     </row>
+    <row r="732" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A732">
+        <v>731</v>
+      </c>
+      <c r="B732">
+        <v>13</v>
+      </c>
+      <c r="C732">
+        <v>4</v>
+      </c>
+      <c r="D732">
+        <v>2</v>
+      </c>
+      <c r="E732">
+        <v>0</v>
+      </c>
+      <c r="F732">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="733" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A733">
+        <v>732</v>
+      </c>
+      <c r="B733">
+        <v>12</v>
+      </c>
+      <c r="C733">
+        <v>11</v>
+      </c>
+      <c r="D733">
+        <v>0</v>
+      </c>
+      <c r="E733">
+        <v>0</v>
+      </c>
+      <c r="F733">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="734" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A734">
+        <v>733</v>
+      </c>
+      <c r="B734">
+        <v>2</v>
+      </c>
+      <c r="C734">
+        <v>26</v>
+      </c>
+      <c r="D734">
+        <v>10</v>
+      </c>
+      <c r="E734">
+        <v>0</v>
+      </c>
+      <c r="F734">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="735" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A735">
+        <v>734</v>
+      </c>
+      <c r="B735">
+        <v>11</v>
+      </c>
+      <c r="C735">
+        <v>7</v>
+      </c>
+      <c r="D735">
+        <v>19</v>
+      </c>
+      <c r="E735">
+        <v>0</v>
+      </c>
+      <c r="F735">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="736" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A736">
+        <v>735</v>
+      </c>
+      <c r="B736">
+        <v>7</v>
+      </c>
+      <c r="C736">
+        <v>15</v>
+      </c>
+      <c r="D736">
+        <v>11</v>
+      </c>
+      <c r="E736">
+        <v>0</v>
+      </c>
+      <c r="F736">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="737" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A737">
+        <v>736</v>
+      </c>
+      <c r="B737">
+        <v>1</v>
+      </c>
+      <c r="C737">
+        <v>6</v>
+      </c>
+      <c r="D737">
+        <v>10</v>
+      </c>
+      <c r="E737">
+        <v>250</v>
+      </c>
+      <c r="F737">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A738">
+        <v>737</v>
+      </c>
+      <c r="B738">
+        <v>11</v>
+      </c>
+      <c r="C738">
+        <v>18</v>
+      </c>
+      <c r="D738">
+        <v>6</v>
+      </c>
+      <c r="E738">
+        <v>0</v>
+      </c>
+      <c r="F738">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="739" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A739">
+        <v>738</v>
+      </c>
+      <c r="B739">
+        <v>5</v>
+      </c>
+      <c r="C739">
+        <v>27</v>
+      </c>
+      <c r="D739">
+        <v>17</v>
+      </c>
+      <c r="E739">
+        <v>0</v>
+      </c>
+      <c r="F739">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="740" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A740">
+        <v>739</v>
+      </c>
+      <c r="B740">
+        <v>3</v>
+      </c>
+      <c r="C740">
+        <v>20</v>
+      </c>
+      <c r="D740">
+        <v>3</v>
+      </c>
+      <c r="E740">
+        <v>0</v>
+      </c>
+      <c r="F740">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="741" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A741">
+        <v>740</v>
+      </c>
+      <c r="B741">
+        <v>6</v>
+      </c>
+      <c r="C741">
+        <v>6</v>
+      </c>
+      <c r="D741">
+        <v>32</v>
+      </c>
+      <c r="E741">
+        <v>250</v>
+      </c>
+      <c r="F741">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="742" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A742">
+        <v>741</v>
+      </c>
+      <c r="B742">
+        <v>2</v>
+      </c>
+      <c r="C742">
+        <v>7</v>
+      </c>
+      <c r="D742">
+        <v>3</v>
+      </c>
+      <c r="E742">
+        <v>0</v>
+      </c>
+      <c r="F742">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="743" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A743">
+        <v>742</v>
+      </c>
+      <c r="B743">
+        <v>11</v>
+      </c>
+      <c r="C743">
+        <v>6</v>
+      </c>
+      <c r="D743">
+        <v>42</v>
+      </c>
+      <c r="E743">
+        <v>0</v>
+      </c>
+      <c r="F743">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="744" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A744">
+        <v>743</v>
+      </c>
+      <c r="B744">
+        <v>2</v>
+      </c>
+      <c r="C744">
+        <v>24</v>
+      </c>
+      <c r="D744">
+        <v>16</v>
+      </c>
+      <c r="E744">
+        <v>0</v>
+      </c>
+      <c r="F744">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="745" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A745">
+        <v>744</v>
+      </c>
+      <c r="B745">
+        <v>11</v>
+      </c>
+      <c r="C745">
+        <v>7</v>
+      </c>
+      <c r="D745">
+        <v>11</v>
+      </c>
+      <c r="E745">
+        <v>0</v>
+      </c>
+      <c r="F745">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="746" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A746">
+        <v>745</v>
+      </c>
+      <c r="B746">
+        <v>16</v>
+      </c>
+      <c r="C746">
+        <v>4</v>
+      </c>
+      <c r="D746">
+        <v>26</v>
+      </c>
+      <c r="E746">
+        <v>0</v>
+      </c>
+      <c r="F746">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="747" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A747">
+        <v>746</v>
+      </c>
+      <c r="B747">
+        <v>27</v>
+      </c>
+      <c r="C747">
+        <v>31</v>
+      </c>
+      <c r="D747">
+        <v>15</v>
+      </c>
+      <c r="E747">
+        <v>0</v>
+      </c>
+      <c r="F747">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="748" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A748">
+        <v>747</v>
+      </c>
+      <c r="B748">
+        <v>4</v>
+      </c>
+      <c r="C748">
+        <v>24</v>
+      </c>
+      <c r="D748">
+        <v>12</v>
+      </c>
+      <c r="E748">
+        <v>0</v>
+      </c>
+      <c r="F748">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="749" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A749">
+        <v>748</v>
+      </c>
+      <c r="B749">
+        <v>18</v>
+      </c>
+      <c r="C749">
+        <v>9</v>
+      </c>
+      <c r="D749">
+        <v>13</v>
+      </c>
+      <c r="E749">
+        <v>0</v>
+      </c>
+      <c r="F749">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="750" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A750">
+        <v>749</v>
+      </c>
+      <c r="B750">
+        <v>9</v>
+      </c>
+      <c r="C750">
+        <v>16</v>
+      </c>
+      <c r="D750">
+        <v>4</v>
+      </c>
+      <c r="E750">
+        <v>0</v>
+      </c>
+      <c r="F750">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="751" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A751">
+        <v>750</v>
+      </c>
+      <c r="B751">
+        <v>23</v>
+      </c>
+      <c r="C751">
+        <v>13</v>
+      </c>
+      <c r="D751">
+        <v>9</v>
+      </c>
+      <c r="E751">
+        <v>250</v>
+      </c>
+      <c r="F751">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="752" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A752">
+        <v>751</v>
+      </c>
+      <c r="B752">
+        <v>9</v>
+      </c>
+      <c r="C752">
+        <v>54</v>
+      </c>
+      <c r="D752">
+        <v>4</v>
+      </c>
+      <c r="E752">
+        <v>0</v>
+      </c>
+      <c r="F752">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="753" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A753">
+        <v>752</v>
+      </c>
+      <c r="B753">
+        <v>18</v>
+      </c>
+      <c r="C753">
+        <v>13</v>
+      </c>
+      <c r="D753">
+        <v>48</v>
+      </c>
+      <c r="E753">
+        <v>0</v>
+      </c>
+      <c r="F753">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="754" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A754">
+        <v>753</v>
+      </c>
+      <c r="B754">
+        <v>15</v>
+      </c>
+      <c r="C754">
+        <v>40</v>
+      </c>
+      <c r="D754">
+        <v>20</v>
+      </c>
+      <c r="E754">
+        <v>250</v>
+      </c>
+      <c r="F754">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="755" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A755">
+        <v>754</v>
+      </c>
+      <c r="B755">
+        <v>4</v>
+      </c>
+      <c r="C755">
+        <v>5</v>
+      </c>
+      <c r="D755">
+        <v>3</v>
+      </c>
+      <c r="E755">
+        <v>0</v>
+      </c>
+      <c r="F755">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="756" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A756">
+        <v>755</v>
+      </c>
+      <c r="B756">
+        <v>7</v>
+      </c>
+      <c r="C756">
+        <v>4</v>
+      </c>
+      <c r="D756">
+        <v>14</v>
+      </c>
+      <c r="E756">
+        <v>0</v>
+      </c>
+      <c r="F756">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="757" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A757">
+        <v>756</v>
+      </c>
+      <c r="B757">
+        <v>7</v>
+      </c>
+      <c r="C757">
+        <v>10</v>
+      </c>
+      <c r="D757">
+        <v>0</v>
+      </c>
+      <c r="E757">
+        <v>0</v>
+      </c>
+      <c r="F757">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="758" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A758">
+        <v>757</v>
+      </c>
+      <c r="B758">
+        <v>16</v>
+      </c>
+      <c r="C758">
+        <v>34</v>
+      </c>
+      <c r="D758">
+        <v>20</v>
+      </c>
+      <c r="E758">
+        <v>0</v>
+      </c>
+      <c r="F758">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="759" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A759">
+        <v>758</v>
+      </c>
+      <c r="B759">
+        <v>5</v>
+      </c>
+      <c r="C759">
+        <v>9</v>
+      </c>
+      <c r="D759">
+        <v>21</v>
+      </c>
+      <c r="E759">
+        <v>0</v>
+      </c>
+      <c r="F759">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="760" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A760">
+        <v>759</v>
+      </c>
+      <c r="B760">
+        <v>7</v>
+      </c>
+      <c r="C760">
+        <v>10</v>
+      </c>
+      <c r="D760">
+        <v>0</v>
+      </c>
+      <c r="E760">
+        <v>0</v>
+      </c>
+      <c r="F760">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="761" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A761">
+        <v>760</v>
+      </c>
+      <c r="B761">
+        <v>6</v>
+      </c>
+      <c r="C761">
+        <v>23</v>
+      </c>
+      <c r="D761">
+        <v>21</v>
+      </c>
+      <c r="E761">
+        <v>0</v>
+      </c>
+      <c r="F761">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="762" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A762">
+        <v>761</v>
+      </c>
+      <c r="B762">
+        <v>8</v>
+      </c>
+      <c r="C762">
+        <v>41</v>
+      </c>
+      <c r="D762">
+        <v>24</v>
+      </c>
+      <c r="E762">
+        <v>0</v>
+      </c>
+      <c r="F762">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="763" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A763">
+        <v>762</v>
+      </c>
+      <c r="B763">
+        <v>6</v>
+      </c>
+      <c r="C763">
+        <v>11</v>
+      </c>
+      <c r="D763">
+        <v>10</v>
+      </c>
+      <c r="E763">
+        <v>0</v>
+      </c>
+      <c r="F763">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="764" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A764">
+        <v>763</v>
+      </c>
+      <c r="B764">
+        <v>7</v>
+      </c>
+      <c r="C764">
+        <v>4</v>
+      </c>
+      <c r="D764">
+        <v>7</v>
+      </c>
+      <c r="E764">
+        <v>250</v>
+      </c>
+      <c r="F764">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="765" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A765">
+        <v>764</v>
+      </c>
+      <c r="B765">
+        <v>6</v>
+      </c>
+      <c r="C765">
+        <v>14</v>
+      </c>
+      <c r="D765">
+        <v>42</v>
+      </c>
+      <c r="E765">
+        <v>0</v>
+      </c>
+      <c r="F765">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="766" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A766">
+        <v>765</v>
+      </c>
+      <c r="B766">
+        <v>8</v>
+      </c>
+      <c r="C766">
+        <v>11</v>
+      </c>
+      <c r="D766">
+        <v>16</v>
+      </c>
+      <c r="E766">
+        <v>250</v>
+      </c>
+      <c r="F766">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="767" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A767">
+        <v>766</v>
+      </c>
+      <c r="B767">
+        <v>21</v>
+      </c>
+      <c r="C767">
+        <v>39</v>
+      </c>
+      <c r="D767">
+        <v>8</v>
+      </c>
+      <c r="E767">
+        <v>250</v>
+      </c>
+      <c r="F767">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="768" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A768">
+        <v>767</v>
+      </c>
+      <c r="B768">
+        <v>15</v>
+      </c>
+      <c r="C768">
+        <v>5</v>
+      </c>
+      <c r="D768">
+        <v>0</v>
+      </c>
+      <c r="E768">
+        <v>250</v>
+      </c>
+      <c r="F768">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="769" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A769">
+        <v>768</v>
+      </c>
+      <c r="B769">
+        <v>9</v>
+      </c>
+      <c r="C769">
+        <v>18</v>
+      </c>
+      <c r="D769">
+        <v>15</v>
+      </c>
+      <c r="E769">
+        <v>0</v>
+      </c>
+      <c r="F769">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="770" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A770">
+        <v>769</v>
+      </c>
+      <c r="B770">
+        <v>31</v>
+      </c>
+      <c r="C770">
+        <v>37</v>
+      </c>
+      <c r="D770">
+        <v>45</v>
+      </c>
+      <c r="E770">
+        <v>0</v>
+      </c>
+      <c r="F770">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="771" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A771">
+        <v>770</v>
+      </c>
+      <c r="B771">
+        <v>16</v>
+      </c>
+      <c r="C771">
+        <v>18</v>
+      </c>
+      <c r="D771">
+        <v>6</v>
+      </c>
+      <c r="E771">
+        <v>0</v>
+      </c>
+      <c r="F771">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="772" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A772">
+        <v>771</v>
+      </c>
+      <c r="B772">
+        <v>12</v>
+      </c>
+      <c r="C772">
+        <v>16</v>
+      </c>
+      <c r="D772">
+        <v>0</v>
+      </c>
+      <c r="E772">
+        <v>0</v>
+      </c>
+      <c r="F772">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="773" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A773">
+        <v>772</v>
+      </c>
+      <c r="B773">
+        <v>2</v>
+      </c>
+      <c r="C773">
+        <v>19</v>
+      </c>
+      <c r="D773">
+        <v>3</v>
+      </c>
+      <c r="E773">
+        <v>0</v>
+      </c>
+      <c r="F773">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="774" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A774">
+        <v>773</v>
+      </c>
+      <c r="B774">
+        <v>12</v>
+      </c>
+      <c r="C774">
+        <v>19</v>
+      </c>
+      <c r="D774">
+        <v>13</v>
+      </c>
+      <c r="E774">
+        <v>0</v>
+      </c>
+      <c r="F774">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="775" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A775">
+        <v>774</v>
+      </c>
+      <c r="B775">
+        <v>30</v>
+      </c>
+      <c r="C775">
+        <v>38</v>
+      </c>
+      <c r="D775">
+        <v>50</v>
+      </c>
+      <c r="E775">
+        <v>0</v>
+      </c>
+      <c r="F775">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="776" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A776">
+        <v>775</v>
+      </c>
+      <c r="B776">
+        <v>31</v>
+      </c>
+      <c r="C776">
+        <v>39</v>
+      </c>
+      <c r="D776">
+        <v>33</v>
+      </c>
+      <c r="E776">
+        <v>0</v>
+      </c>
+      <c r="F776">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="777" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A777">
+        <v>776</v>
+      </c>
+      <c r="B777">
+        <v>13</v>
+      </c>
+      <c r="C777">
+        <v>10</v>
+      </c>
+      <c r="D777">
+        <v>0</v>
+      </c>
+      <c r="E777">
+        <v>0</v>
+      </c>
+      <c r="F777">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A778">
+        <v>777</v>
+      </c>
+      <c r="B778">
+        <v>15</v>
+      </c>
+      <c r="C778">
+        <v>17</v>
+      </c>
+      <c r="D778">
+        <v>24</v>
+      </c>
+      <c r="E778">
+        <v>0</v>
+      </c>
+      <c r="F778">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="779" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A779">
+        <v>778</v>
+      </c>
+      <c r="B779">
+        <v>9</v>
+      </c>
+      <c r="C779">
+        <v>10</v>
+      </c>
+      <c r="D779">
+        <v>0</v>
+      </c>
+      <c r="E779">
+        <v>0</v>
+      </c>
+      <c r="F779">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="780" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A780">
+        <v>779</v>
+      </c>
+      <c r="B780">
+        <v>15</v>
+      </c>
+      <c r="C780">
+        <v>11</v>
+      </c>
+      <c r="D780">
+        <v>45</v>
+      </c>
+      <c r="E780">
+        <v>0</v>
+      </c>
+      <c r="F780">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="781" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A781">
+        <v>780</v>
+      </c>
+      <c r="B781">
+        <v>27</v>
+      </c>
+      <c r="C781">
+        <v>49</v>
+      </c>
+      <c r="D781">
+        <v>16</v>
+      </c>
+      <c r="E781">
+        <v>0</v>
+      </c>
+      <c r="F781">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="782" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A782">
+        <v>781</v>
+      </c>
+      <c r="B782">
+        <v>61</v>
+      </c>
+      <c r="C782">
+        <v>40</v>
+      </c>
+      <c r="D782">
+        <v>55</v>
+      </c>
+      <c r="E782">
+        <v>0</v>
+      </c>
+      <c r="F782">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="783" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A783">
+        <v>782</v>
+      </c>
+      <c r="B783">
+        <v>15</v>
+      </c>
+      <c r="C783">
+        <v>25</v>
+      </c>
+      <c r="D783">
+        <v>32</v>
+      </c>
+      <c r="E783">
+        <v>250</v>
+      </c>
+      <c r="F783">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="784" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A784">
+        <v>783</v>
+      </c>
+      <c r="B784">
+        <v>13</v>
+      </c>
+      <c r="C784">
+        <v>10</v>
+      </c>
+      <c r="D784">
+        <v>16</v>
+      </c>
+      <c r="E784">
+        <v>0</v>
+      </c>
+      <c r="F784">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="785" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A785">
+        <v>784</v>
+      </c>
+      <c r="B785">
+        <v>8</v>
+      </c>
+      <c r="C785">
+        <v>19</v>
+      </c>
+      <c r="D785">
+        <v>18</v>
+      </c>
+      <c r="E785">
+        <v>0</v>
+      </c>
+      <c r="F785">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="786" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A786">
+        <v>785</v>
+      </c>
+      <c r="B786">
+        <v>18</v>
+      </c>
+      <c r="C786">
+        <v>21</v>
+      </c>
+      <c r="D786">
+        <v>2</v>
+      </c>
+      <c r="E786">
+        <v>0</v>
+      </c>
+      <c r="F786">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="787" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A787">
+        <v>786</v>
+      </c>
+      <c r="B787">
+        <v>8</v>
+      </c>
+      <c r="C787">
+        <v>29</v>
+      </c>
+      <c r="D787">
+        <v>13</v>
+      </c>
+      <c r="E787">
+        <v>0</v>
+      </c>
+      <c r="F787">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="788" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A788">
+        <v>787</v>
+      </c>
+      <c r="B788">
+        <v>18</v>
+      </c>
+      <c r="C788">
+        <v>17</v>
+      </c>
+      <c r="D788">
+        <v>41</v>
+      </c>
+      <c r="E788">
+        <v>0</v>
+      </c>
+      <c r="F788">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="789" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A789">
+        <v>788</v>
+      </c>
+      <c r="B789">
+        <v>31</v>
+      </c>
+      <c r="C789">
+        <v>29</v>
+      </c>
+      <c r="D789">
+        <v>37</v>
+      </c>
+      <c r="E789">
+        <v>0</v>
+      </c>
+      <c r="F789">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="790" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A790">
+        <v>789</v>
+      </c>
+      <c r="B790">
+        <v>40</v>
+      </c>
+      <c r="C790">
+        <v>32</v>
+      </c>
+      <c r="D790">
+        <v>21</v>
+      </c>
+      <c r="E790">
+        <v>0</v>
+      </c>
+      <c r="F790">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A791">
+        <v>790</v>
+      </c>
+      <c r="B791">
+        <v>23</v>
+      </c>
+      <c r="C791">
+        <v>8</v>
+      </c>
+      <c r="D791">
+        <v>5</v>
+      </c>
+      <c r="E791">
+        <v>0</v>
+      </c>
+      <c r="F791">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="792" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A792">
+        <v>791</v>
+      </c>
+      <c r="B792">
+        <v>4</v>
+      </c>
+      <c r="C792">
+        <v>24</v>
+      </c>
+      <c r="D792">
+        <v>0</v>
+      </c>
+      <c r="E792">
+        <v>0</v>
+      </c>
+      <c r="F792">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="793" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A793">
+        <v>792</v>
+      </c>
+      <c r="B793">
+        <v>19</v>
+      </c>
+      <c r="C793">
+        <v>31</v>
+      </c>
+      <c r="D793">
+        <v>0</v>
+      </c>
+      <c r="E793">
+        <v>0</v>
+      </c>
+      <c r="F793">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="794" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A794">
+        <v>793</v>
+      </c>
+      <c r="B794">
+        <v>25</v>
+      </c>
+      <c r="C794">
+        <v>26</v>
+      </c>
+      <c r="D794">
+        <v>16</v>
+      </c>
+      <c r="E794">
+        <v>0</v>
+      </c>
+      <c r="F794">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="795" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A795">
+        <v>794</v>
+      </c>
+      <c r="B795">
+        <v>26</v>
+      </c>
+      <c r="C795">
+        <v>33</v>
+      </c>
+      <c r="D795">
+        <v>7</v>
+      </c>
+      <c r="E795">
+        <v>0</v>
+      </c>
+      <c r="F795">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="796" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A796">
+        <v>795</v>
+      </c>
+      <c r="B796">
+        <v>39</v>
+      </c>
+      <c r="C796">
+        <v>33</v>
+      </c>
+      <c r="D796">
+        <v>22</v>
+      </c>
+      <c r="E796">
+        <v>0</v>
+      </c>
+      <c r="F796">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A797">
+        <v>796</v>
+      </c>
+      <c r="B797">
+        <v>28</v>
+      </c>
+      <c r="C797">
+        <v>39</v>
+      </c>
+      <c r="D797">
+        <v>8</v>
+      </c>
+      <c r="E797">
+        <v>250</v>
+      </c>
+      <c r="F797">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A798">
+        <v>797</v>
+      </c>
+      <c r="B798">
+        <v>29</v>
+      </c>
+      <c r="C798">
+        <v>29</v>
+      </c>
+      <c r="D798">
+        <v>42</v>
+      </c>
+      <c r="E798">
+        <v>0</v>
+      </c>
+      <c r="F798">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A799">
+        <v>798</v>
+      </c>
+      <c r="B799">
+        <v>45</v>
+      </c>
+      <c r="C799">
+        <v>27</v>
+      </c>
+      <c r="D799">
+        <v>36</v>
+      </c>
+      <c r="E799">
+        <v>0</v>
+      </c>
+      <c r="F799">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="800" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A800">
+        <v>799</v>
+      </c>
+      <c r="B800">
+        <v>23</v>
+      </c>
+      <c r="C800">
+        <v>52</v>
+      </c>
+      <c r="D800">
+        <v>1</v>
+      </c>
+      <c r="E800">
+        <v>0</v>
+      </c>
+      <c r="F800">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="801" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A801">
+        <v>800</v>
+      </c>
+      <c r="B801">
+        <v>25</v>
+      </c>
+      <c r="C801">
+        <v>19</v>
+      </c>
+      <c r="D801">
+        <v>18</v>
+      </c>
+      <c r="E801">
+        <v>0</v>
+      </c>
+      <c r="F801">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="802" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A802">
+        <v>801</v>
+      </c>
+      <c r="B802">
+        <v>18</v>
+      </c>
+      <c r="C802">
+        <v>27</v>
+      </c>
+      <c r="D802">
+        <v>2</v>
+      </c>
+      <c r="E802">
+        <v>0</v>
+      </c>
+      <c r="F802">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="803" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A803">
+        <v>802</v>
+      </c>
+      <c r="B803">
+        <v>42</v>
+      </c>
+      <c r="C803">
+        <v>19</v>
+      </c>
+      <c r="D803">
+        <v>0</v>
+      </c>
+      <c r="E803">
+        <v>0</v>
+      </c>
+      <c r="F803">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="804" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A804">
+        <v>803</v>
+      </c>
+      <c r="B804">
+        <v>30</v>
+      </c>
+      <c r="C804">
+        <v>12</v>
+      </c>
+      <c r="D804">
+        <v>13</v>
+      </c>
+      <c r="E804">
+        <v>0</v>
+      </c>
+      <c r="F804">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="805" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A805">
+        <v>804</v>
+      </c>
+      <c r="B805">
+        <v>43</v>
+      </c>
+      <c r="C805">
+        <v>39</v>
+      </c>
+      <c r="D805">
+        <v>29</v>
+      </c>
+      <c r="E805">
+        <v>0</v>
+      </c>
+      <c r="F805">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="806" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A806">
+        <v>805</v>
+      </c>
+      <c r="B806">
+        <v>33</v>
+      </c>
+      <c r="C806">
+        <v>5</v>
+      </c>
+      <c r="D806">
+        <v>11</v>
+      </c>
+      <c r="E806">
+        <v>0</v>
+      </c>
+      <c r="F806">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="807" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A807">
+        <v>806</v>
+      </c>
+      <c r="B807">
+        <v>49</v>
+      </c>
+      <c r="C807">
+        <v>37</v>
+      </c>
+      <c r="D807">
+        <v>4</v>
+      </c>
+      <c r="E807">
+        <v>0</v>
+      </c>
+      <c r="F807">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="808" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A808">
+        <v>807</v>
+      </c>
+      <c r="B808">
+        <v>24</v>
+      </c>
+      <c r="C808">
+        <v>62</v>
+      </c>
+      <c r="D808">
+        <v>57</v>
+      </c>
+      <c r="E808">
+        <v>0</v>
+      </c>
+      <c r="F808">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="809" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A809">
+        <v>808</v>
+      </c>
+      <c r="B809">
+        <v>23</v>
+      </c>
+      <c r="C809">
+        <v>7</v>
+      </c>
+      <c r="D809">
+        <v>46</v>
+      </c>
+      <c r="E809">
+        <v>0</v>
+      </c>
+      <c r="F809">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="810" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A810">
+        <v>809</v>
+      </c>
+      <c r="B810">
+        <v>42</v>
+      </c>
+      <c r="C810">
+        <v>24</v>
+      </c>
+      <c r="D810">
+        <v>28</v>
+      </c>
+      <c r="E810">
+        <v>0</v>
+      </c>
+      <c r="F810">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="811" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A811">
+        <v>810</v>
+      </c>
+      <c r="B811">
+        <v>25</v>
+      </c>
+      <c r="C811">
+        <v>46</v>
+      </c>
+      <c r="D811">
+        <v>2</v>
+      </c>
+      <c r="E811">
+        <v>0</v>
+      </c>
+      <c r="F811">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="812" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A812">
+        <v>811</v>
+      </c>
+      <c r="B812">
+        <v>26</v>
+      </c>
+      <c r="C812">
+        <v>39</v>
+      </c>
+      <c r="D812">
+        <v>64</v>
+      </c>
+      <c r="E812">
+        <v>0</v>
+      </c>
+      <c r="F812">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="813" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A813">
+        <v>812</v>
+      </c>
+      <c r="B813">
+        <v>49</v>
+      </c>
+      <c r="C813">
+        <v>62</v>
+      </c>
+      <c r="D813">
+        <v>34</v>
+      </c>
+      <c r="E813">
+        <v>0</v>
+      </c>
+      <c r="F813">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="814" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A814">
+        <v>813</v>
+      </c>
+      <c r="B814">
+        <v>41</v>
+      </c>
+      <c r="C814">
+        <v>23</v>
+      </c>
+      <c r="D814">
+        <v>1</v>
+      </c>
+      <c r="E814">
+        <v>0</v>
+      </c>
+      <c r="F814">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="815" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A815">
+        <v>814</v>
+      </c>
+      <c r="B815">
+        <v>15</v>
+      </c>
+      <c r="C815">
+        <v>19</v>
+      </c>
+      <c r="D815">
+        <v>0</v>
+      </c>
+      <c r="E815">
+        <v>0</v>
+      </c>
+      <c r="F815">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="816" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A816">
+        <v>815</v>
+      </c>
+      <c r="B816">
+        <v>21</v>
+      </c>
+      <c r="C816">
+        <v>30</v>
+      </c>
+      <c r="D816">
+        <v>12</v>
+      </c>
+      <c r="E816">
+        <v>0</v>
+      </c>
+      <c r="F816">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="817" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A817">
+        <v>816</v>
+      </c>
+      <c r="B817">
+        <v>36</v>
+      </c>
+      <c r="C817">
+        <v>16</v>
+      </c>
+      <c r="D817">
+        <v>22</v>
+      </c>
+      <c r="E817">
+        <v>0</v>
+      </c>
+      <c r="F817">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A818">
+        <v>817</v>
+      </c>
+      <c r="B818">
+        <v>39</v>
+      </c>
+      <c r="C818">
+        <v>36</v>
+      </c>
+      <c r="D818">
+        <v>20</v>
+      </c>
+      <c r="E818">
+        <v>0</v>
+      </c>
+      <c r="F818">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A819">
+        <v>818</v>
+      </c>
+      <c r="B819">
+        <v>11</v>
+      </c>
+      <c r="C819">
+        <v>16</v>
+      </c>
+      <c r="D819">
+        <v>13</v>
+      </c>
+      <c r="E819">
+        <v>0</v>
+      </c>
+      <c r="F819">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="820" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A820">
+        <v>819</v>
+      </c>
+      <c r="B820">
+        <v>42</v>
+      </c>
+      <c r="C820">
+        <v>43</v>
+      </c>
+      <c r="D820">
+        <v>57</v>
+      </c>
+      <c r="E820">
+        <v>0</v>
+      </c>
+      <c r="F820">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="821" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A821">
+        <v>820</v>
+      </c>
+      <c r="B821">
+        <v>40</v>
+      </c>
+      <c r="C821">
+        <v>19</v>
+      </c>
+      <c r="D821">
+        <v>31</v>
+      </c>
+      <c r="E821">
+        <v>0</v>
+      </c>
+      <c r="F821">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="822" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A822">
+        <v>821</v>
+      </c>
+      <c r="B822">
+        <v>13</v>
+      </c>
+      <c r="C822">
+        <v>29</v>
+      </c>
+      <c r="D822">
+        <v>10</v>
+      </c>
+      <c r="E822">
+        <v>0</v>
+      </c>
+      <c r="F822">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="823" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A823">
+        <v>822</v>
+      </c>
+      <c r="B823">
+        <v>39</v>
+      </c>
+      <c r="C823">
+        <v>37</v>
+      </c>
+      <c r="D823">
+        <v>38</v>
+      </c>
+      <c r="E823">
+        <v>0</v>
+      </c>
+      <c r="F823">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="824" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A824">
+        <v>823</v>
+      </c>
+      <c r="B824">
+        <v>30</v>
+      </c>
+      <c r="C824">
+        <v>32</v>
+      </c>
+      <c r="D824">
+        <v>16</v>
+      </c>
+      <c r="E824">
+        <v>0</v>
+      </c>
+      <c r="F824">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="825" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A825">
+        <v>824</v>
+      </c>
+      <c r="B825">
+        <v>21</v>
+      </c>
+      <c r="C825">
+        <v>16</v>
+      </c>
+      <c r="D825">
+        <v>0</v>
+      </c>
+      <c r="E825">
+        <v>0</v>
+      </c>
+      <c r="F825">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A826">
+        <v>825</v>
+      </c>
+      <c r="B826">
+        <v>48</v>
+      </c>
+      <c r="C826">
+        <v>47</v>
+      </c>
+      <c r="D826">
+        <v>66</v>
+      </c>
+      <c r="E826">
+        <v>0</v>
+      </c>
+      <c r="F826">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A827">
+        <v>826</v>
+      </c>
+      <c r="B827">
+        <v>45</v>
+      </c>
+      <c r="C827">
+        <v>14</v>
+      </c>
+      <c r="D827">
+        <v>59</v>
+      </c>
+      <c r="E827">
+        <v>0</v>
+      </c>
+      <c r="F827">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A828">
+        <v>827</v>
+      </c>
+      <c r="B828">
+        <v>17</v>
+      </c>
+      <c r="C828">
+        <v>26</v>
+      </c>
+      <c r="D828">
+        <v>4</v>
+      </c>
+      <c r="E828">
+        <v>250</v>
+      </c>
+      <c r="F828">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A829">
+        <v>828</v>
+      </c>
+      <c r="B829">
+        <v>67</v>
+      </c>
+      <c r="C829">
+        <v>27</v>
+      </c>
+      <c r="D829">
+        <v>38</v>
+      </c>
+      <c r="E829">
+        <v>0</v>
+      </c>
+      <c r="F829">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A830">
+        <v>829</v>
+      </c>
+      <c r="B830">
+        <v>36</v>
+      </c>
+      <c r="C830">
+        <v>25</v>
+      </c>
+      <c r="D830">
+        <v>41</v>
+      </c>
+      <c r="E830">
+        <v>0</v>
+      </c>
+      <c r="F830">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A831">
+        <v>830</v>
+      </c>
+      <c r="B831">
+        <v>36</v>
+      </c>
+      <c r="C831">
+        <v>34</v>
+      </c>
+      <c r="D831">
+        <v>15</v>
+      </c>
+      <c r="E831">
+        <v>0</v>
+      </c>
+      <c r="F831">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A832">
+        <v>831</v>
+      </c>
+      <c r="B832">
+        <v>81</v>
+      </c>
+      <c r="C832">
+        <v>29</v>
+      </c>
+      <c r="D832">
+        <v>2</v>
+      </c>
+      <c r="E832">
+        <v>0</v>
+      </c>
+      <c r="F832">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="833" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A833">
+        <v>832</v>
+      </c>
+      <c r="B833">
+        <v>32</v>
+      </c>
+      <c r="C833">
+        <v>35</v>
+      </c>
+      <c r="D833">
+        <v>10</v>
+      </c>
+      <c r="E833">
+        <v>0</v>
+      </c>
+      <c r="F833">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="834" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A834">
+        <v>833</v>
+      </c>
+      <c r="B834">
+        <v>63</v>
+      </c>
+      <c r="C834">
+        <v>27</v>
+      </c>
+      <c r="D834">
+        <v>0</v>
+      </c>
+      <c r="E834">
+        <v>0</v>
+      </c>
+      <c r="F834">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="835" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A835">
+        <v>834</v>
+      </c>
+      <c r="B835">
+        <v>55</v>
+      </c>
+      <c r="C835">
+        <v>97</v>
+      </c>
+      <c r="D835">
+        <v>0</v>
+      </c>
+      <c r="E835">
+        <v>0</v>
+      </c>
+      <c r="F835">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A836">
+        <v>835</v>
+      </c>
+      <c r="B836">
+        <v>58</v>
+      </c>
+      <c r="C836">
+        <v>45</v>
+      </c>
+      <c r="D836">
+        <v>40</v>
+      </c>
+      <c r="E836">
+        <v>0</v>
+      </c>
+      <c r="F836">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A837">
+        <v>836</v>
+      </c>
+      <c r="B837">
+        <v>49</v>
+      </c>
+      <c r="C837">
+        <v>15</v>
+      </c>
+      <c r="D837">
+        <v>61</v>
+      </c>
+      <c r="E837">
+        <v>250</v>
+      </c>
+      <c r="F837">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A838">
+        <v>837</v>
+      </c>
+      <c r="B838">
+        <v>62</v>
+      </c>
+      <c r="C838">
+        <v>9</v>
+      </c>
+      <c r="D838">
+        <v>0</v>
+      </c>
+      <c r="E838">
+        <v>0</v>
+      </c>
+      <c r="F838">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A839">
+        <v>838</v>
+      </c>
+      <c r="B839">
+        <v>86</v>
+      </c>
+      <c r="C839">
+        <v>33</v>
+      </c>
+      <c r="D839">
+        <v>23</v>
+      </c>
+      <c r="E839">
+        <v>0</v>
+      </c>
+      <c r="F839">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A840">
+        <v>839</v>
+      </c>
+      <c r="B840">
+        <v>64</v>
+      </c>
+      <c r="C840">
+        <v>29</v>
+      </c>
+      <c r="D840">
+        <v>7</v>
+      </c>
+      <c r="E840">
+        <v>0</v>
+      </c>
+      <c r="F840">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A841">
+        <v>840</v>
+      </c>
+      <c r="B841">
+        <v>86</v>
+      </c>
+      <c r="C841">
+        <v>45</v>
+      </c>
+      <c r="D841">
+        <v>0</v>
+      </c>
+      <c r="E841">
+        <v>0</v>
+      </c>
+      <c r="F841">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A842">
+        <v>841</v>
+      </c>
+      <c r="B842">
+        <v>53</v>
+      </c>
+      <c r="C842">
+        <v>25</v>
+      </c>
+      <c r="D842">
+        <v>5</v>
+      </c>
+      <c r="E842">
+        <v>0</v>
+      </c>
+      <c r="F842">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A843">
+        <v>842</v>
+      </c>
+      <c r="B843">
+        <v>65</v>
+      </c>
+      <c r="C843">
+        <v>22</v>
+      </c>
+      <c r="D843">
+        <v>0</v>
+      </c>
+      <c r="E843">
+        <v>0</v>
+      </c>
+      <c r="F843">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A844">
+        <v>843</v>
+      </c>
+      <c r="B844">
+        <v>51</v>
+      </c>
+      <c r="C844">
+        <v>40</v>
+      </c>
+      <c r="D844">
+        <v>50</v>
+      </c>
+      <c r="E844">
+        <v>0</v>
+      </c>
+      <c r="F844">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A845">
+        <v>844</v>
+      </c>
+      <c r="B845">
+        <v>18</v>
+      </c>
+      <c r="C845">
+        <v>16</v>
+      </c>
+      <c r="D845">
+        <v>0</v>
+      </c>
+      <c r="E845">
+        <v>0</v>
+      </c>
+      <c r="F845">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A846">
+        <v>845</v>
+      </c>
+      <c r="B846">
+        <v>60</v>
+      </c>
+      <c r="C846">
+        <v>21</v>
+      </c>
+      <c r="D846">
+        <v>27</v>
+      </c>
+      <c r="E846">
+        <v>0</v>
+      </c>
+      <c r="F846">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A847">
+        <v>846</v>
+      </c>
+      <c r="B847">
+        <v>52</v>
+      </c>
+      <c r="C847">
+        <v>26</v>
+      </c>
+      <c r="D847">
+        <v>7</v>
+      </c>
+      <c r="E847">
+        <v>0</v>
+      </c>
+      <c r="F847">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A848">
+        <v>847</v>
+      </c>
+      <c r="B848">
+        <v>31</v>
+      </c>
+      <c r="C848">
+        <v>46</v>
+      </c>
+      <c r="D848">
+        <v>17</v>
+      </c>
+      <c r="E848">
+        <v>0</v>
+      </c>
+      <c r="F848">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A849">
+        <v>848</v>
+      </c>
+      <c r="B849">
+        <v>40</v>
+      </c>
+      <c r="C849">
+        <v>26</v>
+      </c>
+      <c r="D849">
+        <v>12</v>
+      </c>
+      <c r="E849">
+        <v>0</v>
+      </c>
+      <c r="F849">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A850">
+        <v>849</v>
+      </c>
+      <c r="B850">
+        <v>54</v>
+      </c>
+      <c r="C850">
+        <v>40</v>
+      </c>
+      <c r="D850">
+        <v>5</v>
+      </c>
+      <c r="E850">
+        <v>0</v>
+      </c>
+      <c r="F850">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A851">
+        <v>850</v>
+      </c>
+      <c r="B851">
+        <v>57</v>
+      </c>
+      <c r="C851">
+        <v>32</v>
+      </c>
+      <c r="D851">
+        <v>44</v>
+      </c>
+      <c r="E851">
+        <v>0</v>
+      </c>
+      <c r="F851">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A852">
+        <v>851</v>
+      </c>
+      <c r="B852">
+        <v>67</v>
+      </c>
+      <c r="C852">
+        <v>15</v>
+      </c>
+      <c r="D852">
+        <v>30</v>
+      </c>
+      <c r="E852">
+        <v>0</v>
+      </c>
+      <c r="F852">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A853">
+        <v>852</v>
+      </c>
+      <c r="B853">
+        <v>69</v>
+      </c>
+      <c r="C853">
+        <v>42</v>
+      </c>
+      <c r="D853">
+        <v>8</v>
+      </c>
+      <c r="E853">
+        <v>0</v>
+      </c>
+      <c r="F853">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A854">
+        <v>853</v>
+      </c>
+      <c r="B854">
+        <v>58</v>
+      </c>
+      <c r="C854">
+        <v>25</v>
+      </c>
+      <c r="D854">
+        <v>52</v>
+      </c>
+      <c r="E854">
+        <v>0</v>
+      </c>
+      <c r="F854">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A855">
+        <v>854</v>
+      </c>
+      <c r="B855">
+        <v>47</v>
+      </c>
+      <c r="C855">
+        <v>17</v>
+      </c>
+      <c r="D855">
+        <v>0</v>
+      </c>
+      <c r="E855">
+        <v>0</v>
+      </c>
+      <c r="F855">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A856">
+        <v>855</v>
+      </c>
+      <c r="B856">
+        <v>53</v>
+      </c>
+      <c r="C856">
+        <v>40</v>
+      </c>
+      <c r="D856">
+        <v>27</v>
+      </c>
+      <c r="E856">
+        <v>0</v>
+      </c>
+      <c r="F856">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A857">
+        <v>856</v>
+      </c>
+      <c r="B857">
+        <v>43</v>
+      </c>
+      <c r="C857">
+        <v>89</v>
+      </c>
+      <c r="D857">
+        <v>43</v>
+      </c>
+      <c r="E857">
+        <v>0</v>
+      </c>
+      <c r="F857">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A858">
+        <v>857</v>
+      </c>
+      <c r="B858">
+        <v>54</v>
+      </c>
+      <c r="C858">
+        <v>35</v>
+      </c>
+      <c r="D858">
+        <v>0</v>
+      </c>
+      <c r="E858">
+        <v>0</v>
+      </c>
+      <c r="F858">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A859">
+        <v>858</v>
+      </c>
+      <c r="B859">
+        <v>78</v>
+      </c>
+      <c r="C859">
+        <v>18</v>
+      </c>
+      <c r="D859">
+        <v>0</v>
+      </c>
+      <c r="E859">
+        <v>0</v>
+      </c>
+      <c r="F859">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A860">
+        <v>859</v>
+      </c>
+      <c r="B860">
+        <v>48</v>
+      </c>
+      <c r="C860">
+        <v>31</v>
+      </c>
+      <c r="D860">
+        <v>8</v>
+      </c>
+      <c r="E860">
+        <v>0</v>
+      </c>
+      <c r="F860">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A861">
+        <v>860</v>
+      </c>
+      <c r="B861">
+        <v>29</v>
+      </c>
+      <c r="C861">
+        <v>17</v>
+      </c>
+      <c r="D861">
+        <v>16</v>
+      </c>
+      <c r="E861">
+        <v>0</v>
+      </c>
+      <c r="F861">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A862">
+        <v>861</v>
+      </c>
+      <c r="B862">
+        <v>59</v>
+      </c>
+      <c r="C862">
+        <v>31</v>
+      </c>
+      <c r="D862">
+        <v>15</v>
+      </c>
+      <c r="E862">
+        <v>0</v>
+      </c>
+      <c r="F862">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A863">
+        <v>862</v>
+      </c>
+      <c r="B863">
+        <v>90</v>
+      </c>
+      <c r="C863">
+        <v>12</v>
+      </c>
+      <c r="D863">
+        <v>15</v>
+      </c>
+      <c r="E863">
+        <v>0</v>
+      </c>
+      <c r="F863">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F731"/>
+    <ignoredError sqref="A2:F863 A1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>